--- a/data/daily/2026-08/2026-08-24.xlsx
+++ b/data/daily/2026-08/2026-08-24.xlsx
@@ -1218,27 +1218,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
@@ -1253,34 +1253,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306208&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/wEewWmXsoUl4j1ERyFu9032306208_00_01wEewWmXsoUl4j1ERyFu9.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>스키니랩 프레스팝 멀티비타민 포도 맛 4개입</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>스키니랩</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1303,19 +1303,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=976195494&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260303/LzsQYuxI5fqSY38EGRSf976195494_00_01LzsQYuxI5fqSY38EGRSf.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>안국약품 브이팩 남성용 올인원 멀티 비타민 7포</t>
+          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1373,19 +1373,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235547&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591420&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/jgM8z9lj7cP7W5etxeXM968235547_00_00jgM8z9lj7cP7W5etxeXM.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250514/oMFpSUTevplZ5wvdXiLh591591420_00_00oMFpSUTevplZ5wvdXiLh.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1393,27 +1393,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 아이라이트 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624076&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/zf0uM3McjshpycTXP0T2913624076_00_00zf0uM3McjshpycTXP0T2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1463,34 +1463,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1498,34 +1498,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651654&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/BJcWNz19ajlLYaMbOK0e600651654_00_00BJcWNz19ajlLYaMbOK0e.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 관절 건강 올인원 15포 15일분</t>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991020&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618641&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/yH5aOMk0fGfjGGk0S84s033991020_00_00yH5aOMk0fGfjGGk0S84s.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/m3XnQVGNmWJfQCUZVnvy601618641_00_00m3XnQVGNmWJfQCUZVnvy.jpg</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1724,34 +1724,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>CJ 바이오코어 피부면역유산균 100억 30+10포 / 30캡슐</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>11,910원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265834ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014337ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1759,34 +1759,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>30,900원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265834ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1794,34 +1794,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[서현PICK] 콜레올로지 티 PRO 하비탈출 8,000mg X 7포/15포 (7일분/15일분)</t>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14,700원</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205750&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020575005ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1829,27 +1829,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CJ 바이오코어 피부면역유산균 100억 30+10포 / 30캡슐</t>
+          <t>[서현PICK] 콜레올로지 티 PRO 하비탈출 8,000mg X 7포/15포 (7일분/15일분)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11,910원</t>
+          <t>14,700원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205750&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014337ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020575005ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1899,34 +1899,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>26,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492941ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1934,27 +1934,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[8월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>6,900원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563485ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786103ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2007,45 +2007,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2055,16 +2055,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -2077,25 +2077,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2121,16 +2121,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2149,10 +2149,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2161,7 +2161,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2171,12 +2171,34 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/daily/2026-08/2026-08-24.xlsx
+++ b/data/daily/2026-08/2026-08-24.xlsx
@@ -1,16 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="올리브영" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="카테고리통계" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기_카드형" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰_카드형" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영_카드형" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +23,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +63,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -125,6 +149,2036 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,741 +2470,749 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>상품URL</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>이미지URL</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>34,000원</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/2301047</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260730085615_4b56c128b0dd4f359841aedea29c71a4.jpg</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>옵티젠</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>26,900원</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/7608679</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260819145934_d072478fcfb3490d982fb6787a2dd648.jpg</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>109,000원</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/2484405</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260824085655_412aa44b54824ee1b07e4c6cd17da202.jpg</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>43,900원</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/11866425</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260715133556_5b220cca6be34a0aa6491af5bca27f47.jpg</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>[사은품 증정/센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>센트룸</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>24,000원</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/7320451</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260821174846_45143a0db27240d2a750fe3ec9963935.jpg</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>종근당</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>23,800원</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/7948462</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260814153548_9829675ac5e14db383c0dd63450e48bc.jpg</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>뉴트리포유</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>19,900원</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
         <is>
           <t>홍삼/인삼</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>정관장</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>35,000원</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>닥터블릿</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>52,900원</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>59,800원</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260824090746_aecda274677840e2bce6fa7e201e1caa.jpg</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="38" customHeight="1">
+      <c r="B12" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +9포 추가 +파로저당 견과류바 +파로저당 단백칩 증정</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>45,900원</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260824085804_30591e4d109142fcb7cf529efd3894d8.jpg</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="38" customHeight="1">
+      <c r="B13" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>45,800원</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="38" customHeight="1">
+      <c r="B14" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>65,900원</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="38" customHeight="1">
+      <c r="B15" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>4</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="38" customHeight="1">
+      <c r="B16" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" t="n">
         <v>5</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>27,900원</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17" ht="38" customHeight="1">
+      <c r="B17" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>6</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>삼대오백</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>17,900원</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260701120356_f9d975374d374b858dd4262325030e55.jpg</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="38" customHeight="1">
+      <c r="B18" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="C18" t="n">
         <v>7</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>31,500원</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/10848340</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19" ht="38" customHeight="1">
+      <c r="B19" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>익스트림</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>42,900원</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20" ht="38" customHeight="1">
+      <c r="B20" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="C20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>랩노쉬</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>20,900원</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/12052312</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="38" customHeight="1">
+      <c r="B21" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>10</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>뉴트리디데이</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>30,900원</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/4487367</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
         </is>
@@ -1158,6 +3220,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1167,391 +3230,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>상품URL</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>이미지URL</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>이너뷰 바이 리튠</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
         <is>
           <t>혈행</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>종근당건강</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591420&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20250514/oMFpSUTevplZ5wvdXiLh591591420_00_00oMFpSUTevplZ5wvdXiLh.jpg</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
         <is>
           <t>마그네슘</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>유한양행</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651654&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20260325/BJcWNz19ajlLYaMbOK0e600651654_00_00BJcWNz19ajlLYaMbOK0e.jpg</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
         <is>
           <t>마그네슘</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>동화약품</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618641&amp;recmYn=N</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://cdn.daisomall.co.kr/file/PD/20260406/m3XnQVGNmWJfQCUZVnvy601618641_00_00m3XnQVGNmWJfQCUZVnvy.jpg</t>
         </is>
@@ -1559,6 +3630,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1568,391 +3640,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>상품URL</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>이미지URL</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 60캡슐 (+철분헤모케어 3포) (2개월분)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30,900원</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225566&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022556606ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>[8월 올영픽] 판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>판도라</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>24,500원</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733447ko.png?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CJ 바이오코어 피부면역유산균 100억 30+10포 / 30캡슐</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>바이오코어유산균</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>11,910원</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014337ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>30,900원</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265834ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>49,900원</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>[서현PICK] 콜레올로지 티 PRO 하비탈출 8,000mg X 7포/15포 (7일분/15일분)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>14,700원</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205750&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020575005ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>생활약속</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>14,500원</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012132ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>26,000원</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492941ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>씨제이웰케어</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>6,900원</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786103ko.jpg?l=ko</t>
         </is>
@@ -1960,6 +4040,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2205,4 +4286,1583 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>건강식품·영양제</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>옵티젠</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>센트룸</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>뉴트리포유</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>정관장</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>한국인 맞춤 비타민 옵티젠 이뮨 멀티비타민&amp;미네랄 10입 / 1박스 (+GIFT 쇼핑백)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 슬리브 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[사은품 증정/센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>34,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>26,900원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>109,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>43,900원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>24,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>23,800원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>35,000원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>59,800원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>다이어트·이너뷰티</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>삼대오백</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>랩노쉬</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>뉴트리디데이</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +9포 추가 +파로저당 견과류바 +파로저당 단백칩 증정</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>45,900원</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>45,800원</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>32,900원</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>31,500원</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>20,900원</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>30,900원</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A10:A15"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId20"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>다이소몰</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>판도라</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 60캡슐 (+철분헤모케어 3포) (2개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽] 판도라 브이트리티 7/14+1포 (7/15일분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>CJ 바이오코어 피부면역유산균 100억 30+10포 / 30캡슐</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[서현PICK] 콜레올로지 티 PRO 하비탈출 8,000mg X 7포/15포 (7일분/15일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>30,900원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>24,500원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>32,900원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>11,910원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>30,900원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>49,900원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>14,700원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>14,500원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>26,000원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>6,900원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+</worksheet>
 </file>
--- a/data/daily/2026-08/2026-08-24.xlsx
+++ b/data/daily/2026-08/2026-08-24.xlsx
@@ -4,12 +4,12 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="올리브영" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리통계" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카카오선물하기_카드형" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다이소몰_카드형" sheetId="6" state="visible" r:id="rId6"/>
@@ -174,6 +174,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -199,6 +202,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -224,6 +230,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -249,6 +258,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -274,6 +286,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -299,6 +314,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -324,6 +342,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -349,6 +370,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -374,6 +398,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -399,6 +426,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -424,6 +454,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -449,6 +482,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -474,6 +510,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -499,6 +538,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -524,6 +566,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -549,6 +594,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -574,6 +622,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -599,6 +650,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -624,6 +678,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -649,6 +706,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -679,6 +739,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -704,6 +767,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -729,6 +795,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -754,6 +823,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -779,6 +851,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -804,6 +879,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -829,6 +907,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -854,6 +935,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -879,6 +963,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -904,6 +991,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -934,6 +1024,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -959,6 +1052,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -984,6 +1080,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1009,6 +1108,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1034,6 +1136,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1059,6 +1164,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1084,6 +1192,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1109,6 +1220,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1134,6 +1248,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1159,6 +1276,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1189,6 +1309,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1214,6 +1337,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1239,6 +1365,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1264,6 +1393,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1289,6 +1421,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1314,6 +1449,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1339,6 +1477,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1364,6 +1505,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1389,6 +1533,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1414,6 +1561,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1439,6 +1589,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1464,6 +1617,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1489,6 +1645,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1514,6 +1673,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1539,6 +1701,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1564,6 +1729,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1589,6 +1757,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1614,6 +1785,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1639,6 +1813,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1664,6 +1841,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1694,6 +1874,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1719,6 +1902,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1744,6 +1930,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1769,6 +1958,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1794,6 +1986,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1819,6 +2014,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1844,6 +2042,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1869,6 +2070,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1894,6 +2098,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1919,6 +2126,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1949,6 +2159,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1974,6 +2187,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1999,6 +2215,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2024,6 +2243,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2049,6 +2271,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2074,6 +2299,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2099,6 +2327,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2124,6 +2355,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2149,6 +2383,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2174,6 +2411,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
